--- a/data/trans_dic/P15E_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15E_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,73; 82,46</t>
+          <t>51,15; 82,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,53; 84,38</t>
+          <t>69,35; 83,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68,92; 82,12</t>
+          <t>68,23; 81,92</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,67; 80,15</t>
+          <t>34,68; 79,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,97; 81,19</t>
+          <t>42,07; 79,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,75; 75,87</t>
+          <t>45,64; 74,74</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 100,0</t>
+          <t>7,2; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 69,67</t>
+          <t>13,74; 70,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,9; 69,66</t>
+          <t>20,95; 67,92</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,5; 76,16</t>
+          <t>50,07; 77,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,72; 79,17</t>
+          <t>65,05; 78,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,15; 75,57</t>
+          <t>63,07; 76,26</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10576; 17189</t>
+          <t>10663; 17236</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44559; 53307</t>
+          <t>43814; 53017</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57904; 68995</t>
+          <t>57325; 68831</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3782; 9002</t>
+          <t>3895; 8969</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5727; 10577</t>
+          <t>5481; 10405</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11099; 18406</t>
+          <t>11071; 18132</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76; 2031</t>
+          <t>146; 2031</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>810; 4109</t>
+          <t>810; 4135</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1657; 5523</t>
+          <t>1661; 5384</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17224; 25976</t>
+          <t>17080; 26406</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53953; 64997</t>
+          <t>53408; 64569</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73382; 87822</t>
+          <t>73293; 88618</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15E_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15E_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,15; 82,68</t>
+          <t>51,39; 82,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,35; 83,92</t>
+          <t>70,13; 85,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68,23; 81,92</t>
+          <t>68,51; 81,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,68; 79,85</t>
+          <t>34,13; 81,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,07; 79,87</t>
+          <t>42,29; 79,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,64; 74,74</t>
+          <t>46,17; 75,6</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>49,87%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 100,0</t>
+          <t>14,21; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 70,12</t>
+          <t>20,02; 73,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,95; 67,92</t>
+          <t>26,32; 73,93</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,07; 77,42</t>
+          <t>50,16; 75,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,05; 78,65</t>
+          <t>66,08; 79,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,07; 76,26</t>
+          <t>64,29; 76,75</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49099</t>
+          <t>52667</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63387</t>
+          <t>68032</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10663; 17236</t>
+          <t>11653; 18732</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43814; 53017</t>
+          <t>47060; 57190</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57325; 68831</t>
+          <t>61510; 73605</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>15993</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3895; 8969</t>
+          <t>4162; 9888</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5481; 10405</t>
+          <t>5878; 11088</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11071; 18132</t>
+          <t>12047; 19727</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>5271</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>146; 2031</t>
+          <t>460; 3235</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>810; 4135</t>
+          <t>1469; 5389</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1661; 5384</t>
+          <t>2782; 7815</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>59616</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>89296</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17080; 26406</t>
+          <t>19114; 28837</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53408; 64569</t>
+          <t>58377; 70533</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73293; 88618</t>
+          <t>81289; 97038</t>
         </is>
       </c>
     </row>
